--- a/Manuscript/Manuscript v.2/Supplemental Files/Appendix S1. Statistics.xlsx
+++ b/Manuscript/Manuscript v.2/Supplemental Files/Appendix S1. Statistics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ggraham/Desktop/multiome_poa/Manuscript/Manuscript v.2/Supplemental Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A2CAD21-C429-324B-A232-246A1274CF4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C0EC45-ACAF-FA42-B0A0-63AE23B3AEF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20100" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="268">
   <si>
     <t>Appendix S1. Statistical results</t>
   </si>
@@ -126,12 +126,6 @@
   </si>
   <si>
     <t>Fig. 6D–F: steroid receptor-associated expression in 6_POA_Mixed</t>
-  </si>
-  <si>
-    <t>Other_DEGs</t>
-  </si>
-  <si>
-    <t>Other DEGs cited in the text (igf2bp1, 0_Spall_Mixed)</t>
   </si>
   <si>
     <t>Fig. 1B–C. Behavior, 11-KT, gonadal histology and gonad volume (Table 1)</t>
@@ -1427,12 +1421,8 @@
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>33</v>
-      </c>
+      <c r="A27" s="4"/>
+      <c r="B27" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1461,51 +1451,51 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E5" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C6" s="9">
         <v>10.741774556174679</v>
@@ -1528,10 +1518,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C7" s="9">
         <v>26.329467690314949</v>
@@ -1554,10 +1544,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C8" s="8">
         <v>7.45227093983614</v>
@@ -1580,10 +1570,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C9" s="8">
         <v>9.8204973761573591</v>
@@ -1606,10 +1596,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C10" s="8">
         <v>8.0165265686100557</v>
@@ -1632,10 +1622,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C11" s="9">
         <v>15.646653456763691</v>
@@ -1658,10 +1648,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C12" s="8">
         <v>2.5698707069409998</v>
@@ -1684,10 +1674,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C13" s="9">
         <v>18.731212436368221</v>
@@ -1710,44 +1700,44 @@
     </row>
     <row r="16" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="F17" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E17" s="6" t="s">
+      <c r="G17" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="H17" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="I17" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="G17" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>195</v>
-      </c>
       <c r="J17" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B18" s="8">
         <v>4.6272173480133502E-2</v>
@@ -1779,7 +1769,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B19" s="8">
         <v>0.11850603760478461</v>
@@ -1811,7 +1801,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B20" s="8">
         <v>1.823408375695957E-2</v>
@@ -1843,7 +1833,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B21" s="8">
         <v>3.0384347603674491E-2</v>
@@ -1875,7 +1865,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B22" s="8">
         <v>0.26852516110506419</v>
@@ -1907,7 +1897,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B23" s="8">
         <v>4.3114616490414717E-2</v>
@@ -1939,7 +1929,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B24" s="8">
         <v>6.5586005211997797E-2</v>
@@ -1971,7 +1961,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B25" s="8">
         <v>8.69028349447315E-2</v>
@@ -2003,52 +1993,52 @@
     </row>
     <row r="28" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>39</v>
-      </c>
       <c r="D30" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="I30" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D31" s="9">
         <v>44.231011550418643</v>
@@ -2065,13 +2055,13 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D32" s="8">
         <v>1.611928974890954</v>
@@ -2094,13 +2084,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D33" s="9">
         <v>41.979665446829912</v>
@@ -2117,13 +2107,13 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D34" s="8">
         <v>0.90299594751174783</v>
@@ -2146,13 +2136,13 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D35" s="9">
         <v>62.864708627107603</v>
@@ -2169,13 +2159,13 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D36" s="9">
         <v>11.72245413152786</v>
@@ -2198,13 +2188,13 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D37" s="9">
         <v>90.239009201715476</v>
@@ -2221,13 +2211,13 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D38" s="8">
         <v>0.84104597641134837</v>
@@ -2250,13 +2240,13 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D39" s="9">
         <v>37.44303167323757</v>
@@ -2273,13 +2263,13 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="7" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D40" s="8">
         <v>1.0949047845905151</v>
@@ -2302,44 +2292,44 @@
     </row>
     <row r="43" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B44" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E44" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="F44" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="D44" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E44" s="6" t="s">
+      <c r="G44" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F44" s="6" t="s">
+      <c r="I44" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="G44" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>195</v>
-      </c>
       <c r="J44" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="7" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B45" s="8">
         <v>0.51849395814913057</v>
@@ -2371,7 +2361,7 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B46" s="8">
         <v>0.55299759308380003</v>
@@ -2403,7 +2393,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B47" s="8">
         <v>0.43383436486884758</v>
@@ -2435,7 +2425,7 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B48" s="8">
         <v>0.39633313685037819</v>
@@ -2467,7 +2457,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B49" s="8">
         <v>0.52959770114942528</v>
@@ -2499,70 +2489,70 @@
     </row>
     <row r="52" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E54" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B54" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="C54" s="6" t="s">
+      <c r="F54" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G54" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="D54" s="6" t="s">
+      <c r="H54" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="E54" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G54" s="6" t="s">
+      <c r="I54" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="H54" s="6" t="s">
+      <c r="J54" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="I54" s="6" t="s">
+      <c r="K54" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="J54" s="6" t="s">
+      <c r="L54" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="K54" s="6" t="s">
+      <c r="M54" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="L54" s="6" t="s">
+      <c r="N54" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="M54" s="6" t="s">
+      <c r="O54" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="N54" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="O54" s="6" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D55" s="9">
         <v>17.109998799365489</v>
@@ -2603,13 +2593,13 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D56" s="9">
         <v>21.8896953068577</v>
@@ -2650,13 +2640,13 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D57" s="9">
         <v>17.581605053169891</v>
@@ -2697,13 +2687,13 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D58" s="9">
         <v>15.35738386019519</v>
@@ -2744,13 +2734,13 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D59" s="8">
         <v>2.4719449762946519</v>
@@ -2791,13 +2781,13 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D60" s="9">
         <v>19.498935406073191</v>
@@ -2838,49 +2828,49 @@
     </row>
     <row r="63" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B65" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C65" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="D65" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E65" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D65" s="6" t="s">
+      <c r="F65" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E65" s="6" t="s">
+      <c r="G65" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F65" s="6" t="s">
+      <c r="H65" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G65" s="6" t="s">
+      <c r="I65" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="H65" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="I65" s="6" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="7" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C66" s="8">
         <v>2.6859226833320138</v>
@@ -2906,38 +2896,38 @@
     </row>
     <row r="69" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D71" s="8">
         <v>0.2390847334670671</v>
@@ -2951,13 +2941,13 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D72" s="8">
         <v>0.24241897742250271</v>
@@ -2971,13 +2961,13 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D73" s="8">
         <v>0.358430661546705</v>
@@ -2991,13 +2981,13 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D74" s="8">
         <v>2.7470358675692971E-2</v>
@@ -3011,13 +3001,13 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D75" s="8">
         <v>3.9243316000962293E-2</v>
@@ -3031,13 +3021,13 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D76" s="8">
         <v>9.8526989814916296E-2</v>
@@ -3051,13 +3041,13 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D77" s="8">
         <v>6.2913077619227598E-2</v>
@@ -3071,13 +3061,13 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D78" s="8">
         <v>8.517374196207779E-2</v>
@@ -3091,13 +3081,13 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D79" s="8">
         <v>0.14306664621805529</v>
@@ -3111,13 +3101,13 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D80" s="8">
         <v>0.53269099472701542</v>
@@ -3131,13 +3121,13 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D81" s="8">
         <v>0.41720907780489691</v>
@@ -3151,13 +3141,13 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D82" s="8">
         <v>0.36212228689985271</v>
@@ -3171,13 +3161,13 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D83" s="8">
         <v>7.6222510238276475E-2</v>
@@ -3191,13 +3181,13 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D84" s="8">
         <v>2.91714903135806E-2</v>
@@ -3211,13 +3201,13 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D85" s="8">
         <v>1.3003354176107949E-2</v>
@@ -3231,13 +3221,13 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D86" s="8">
         <v>0.13377979903626711</v>
@@ -3251,13 +3241,13 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D87" s="8">
         <v>8.2778295986640132E-2</v>
@@ -3271,13 +3261,13 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D88" s="8">
         <v>0.24062210097067349</v>
@@ -3291,13 +3281,13 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D89" s="8">
         <v>0.14358479320698911</v>
@@ -3311,13 +3301,13 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D90" s="8">
         <v>0.2163763404454008</v>
@@ -3331,13 +3321,13 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D91" s="8">
         <v>6.0349451503220158E-2</v>
@@ -3370,54 +3360,54 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="I5" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C6" s="8">
         <v>4.6359359743057684</v>
@@ -3443,10 +3433,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C7" s="8">
         <v>1.5842908868303081</v>
@@ -3472,10 +3462,10 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C8" s="8">
         <v>4.5823833922640747</v>
@@ -3501,32 +3491,32 @@
     </row>
     <row r="11" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C13" s="8">
         <v>-7.0102900651476854E-2</v>
@@ -3540,10 +3530,10 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C14" s="8">
         <v>7.267545547473375E-3</v>
@@ -3557,10 +3547,10 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C15" s="8">
         <v>4.5458046956380199E-2</v>
@@ -3574,10 +3564,10 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C16" s="8">
         <v>-7.54614725644326E-2</v>
@@ -3591,10 +3581,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C17" s="8">
         <v>-2.0393482634583671E-2</v>
@@ -3608,10 +3598,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C18" s="8">
         <v>7.0699445455749729E-2</v>
@@ -3625,10 +3615,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C19" s="8">
         <v>-6.0233046237489707E-2</v>
@@ -3642,10 +3632,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C20" s="8">
         <v>-1.800277125044903E-2</v>
@@ -3659,10 +3649,10 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C21" s="8">
         <v>6.3879402280620903E-2</v>
@@ -3696,60 +3686,60 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="E5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="I5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="J5" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>47</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>49</v>
       </c>
       <c r="D6" s="8">
         <v>2.4791809065815831</v>
@@ -3775,13 +3765,13 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D7" s="8">
         <v>3.1267846252742899</v>
@@ -3807,13 +3797,13 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D8" s="9">
         <v>15.16109546099392</v>
@@ -3839,13 +3829,13 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D9" s="9">
         <v>21.973385347999841</v>
@@ -3867,13 +3857,13 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D10" s="9">
         <v>20.34893416937911</v>
@@ -3895,13 +3885,13 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D11" s="8">
         <v>6.8310944024577536</v>
@@ -3923,13 +3913,13 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>58</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>60</v>
       </c>
       <c r="D12" s="8">
         <v>6.9702365136231768</v>
@@ -3949,37 +3939,37 @@
     </row>
     <row r="15" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C17" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C18" s="9">
         <v>369.66666666666669</v>
@@ -3993,10 +3983,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C19" s="9">
         <v>384</v>
@@ -4010,10 +4000,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C20" s="9">
         <v>99</v>
@@ -4027,10 +4017,10 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C21" s="9">
         <v>71</v>
@@ -4044,10 +4034,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C22" s="9">
         <v>542.5</v>
@@ -4061,10 +4051,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C23" s="9">
         <v>167</v>
@@ -4078,10 +4068,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C24" s="9">
         <v>24</v>
@@ -4093,10 +4083,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C25" s="9">
         <v>266</v>
@@ -4108,10 +4098,10 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C26" s="8">
         <v>0.25585711057976068</v>
@@ -4125,10 +4115,10 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C27" s="8">
         <v>-0.1129069113184281</v>
@@ -4142,10 +4132,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C28" s="8">
         <v>-0.22269821434850309</v>
@@ -4159,10 +4149,10 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C29" s="8">
         <v>0.27305046257449878</v>
@@ -4176,10 +4166,10 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C30" s="8">
         <v>-5.9355459087561159E-3</v>
@@ -4193,10 +4183,10 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C31" s="8">
         <v>0.27986338285846901</v>
@@ -4208,10 +4198,10 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C32" s="8">
         <v>0.28048555483333332</v>
@@ -4225,10 +4215,10 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C33" s="8">
         <v>0.67725253228571425</v>
@@ -4242,10 +4232,10 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C34" s="8">
         <v>0.74463718914285715</v>
@@ -4259,10 +4249,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C35" s="8">
         <v>0.44804191650000003</v>
@@ -4276,10 +4266,10 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C36" s="8">
         <v>0.49484245650000003</v>
@@ -4293,10 +4283,10 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C37" s="8">
         <v>0.37796293600000003</v>
@@ -4308,10 +4298,10 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C38" s="8">
         <v>0.66387420350000004</v>
@@ -4325,10 +4315,10 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C39" s="8">
         <v>0.24170744942857139</v>
@@ -4342,10 +4332,10 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C40" s="8">
         <v>0.1628806715714286</v>
@@ -4359,10 +4349,10 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C41" s="8">
         <v>0</v>
@@ -4376,10 +4366,10 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C42" s="8">
         <v>0.45676560900000002</v>
@@ -4393,10 +4383,10 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C43" s="8">
         <v>0.56993129899999995</v>
@@ -4408,10 +4398,10 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C44" s="9">
         <v>514</v>
@@ -4425,10 +4415,10 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C45" s="9">
         <v>477.85714285714278</v>
@@ -4442,10 +4432,10 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C46" s="9">
         <v>222.57142857142861</v>
@@ -4459,10 +4449,10 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C47" s="9">
         <v>296</v>
@@ -4476,10 +4466,10 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C48" s="9">
         <v>544</v>
@@ -4493,10 +4483,10 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C49" s="9">
         <v>304.66666666666669</v>
@@ -4510,10 +4500,10 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C50" s="9">
         <v>45</v>
@@ -4525,10 +4515,10 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C51" s="9">
         <v>480</v>
@@ -4540,10 +4530,10 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C52" s="8">
         <v>2.8298419282</v>
@@ -4557,10 +4547,10 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C53" s="8">
         <v>2.7636879174285709</v>
@@ -4574,10 +4564,10 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C54" s="8">
         <v>2.4997439997142861</v>
@@ -4591,10 +4581,10 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C55" s="8">
         <v>1.616439073</v>
@@ -4608,10 +4598,10 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C56" s="8">
         <v>2.7369508284999999</v>
@@ -4625,10 +4615,10 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C57" s="8">
         <v>1.5314352605999999</v>
@@ -4642,10 +4632,10 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C58" s="8">
         <v>2.0773315609999998</v>
@@ -4657,10 +4647,10 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C59" s="8">
         <v>2.8049908229999998</v>
@@ -4690,60 +4680,60 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="E5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="I5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="J5" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D6" s="9">
         <v>11.83289782741876</v>
@@ -4769,13 +4759,13 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D7" s="9">
         <v>10.04592479309103</v>
@@ -4801,13 +4791,13 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D8" s="8">
         <v>9.4671958181730016</v>
@@ -4827,13 +4817,13 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D9" s="8">
         <v>5.4935525993957297</v>
@@ -4853,13 +4843,13 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D10" s="9">
         <v>169.4156126625042</v>
@@ -4881,13 +4871,13 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D11" s="8">
         <v>4.3600849090304914</v>
@@ -4909,32 +4899,32 @@
     </row>
     <row r="14" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C15" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C16" s="8">
         <v>5.3833333333333337</v>
@@ -4948,10 +4938,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C17" s="8">
         <v>6.6428571428571432</v>
@@ -4965,10 +4955,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C18" s="8">
         <v>5.0714285714285712</v>
@@ -4982,10 +4972,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C19" s="8">
         <v>6.85</v>
@@ -4999,10 +4989,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C20" s="8">
         <v>5.35</v>
@@ -5016,10 +5006,10 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C21" s="8">
         <v>7.75</v>
@@ -5033,10 +5023,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C22" s="8">
         <v>6.8</v>
@@ -5048,10 +5038,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C23" s="8">
         <v>5.3</v>
@@ -5063,10 +5053,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C24" s="8">
         <v>3.1333333333333329</v>
@@ -5080,10 +5070,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C25" s="8">
         <v>5.7</v>
@@ -5097,10 +5087,10 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C26" s="8">
         <v>2.4500000000000002</v>
@@ -5114,10 +5104,10 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C27" s="8">
         <v>6.375</v>
@@ -5131,10 +5121,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C28" s="8">
         <v>2.91</v>
@@ -5148,10 +5138,10 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C29" s="8">
         <v>9.7650000000000006</v>
@@ -5165,10 +5155,10 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C30" s="8">
         <v>6.76</v>
@@ -5180,10 +5170,10 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C31" s="8">
         <v>2.68</v>
@@ -5195,10 +5185,10 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C32" s="9">
         <v>107.3986807142857</v>
@@ -5212,10 +5202,10 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C33" s="9">
         <v>101.9060846571429</v>
@@ -5229,10 +5219,10 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C34" s="9">
         <v>107.03931205000001</v>
@@ -5246,10 +5236,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C35" s="9">
         <v>101.91885965</v>
@@ -5263,10 +5253,10 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C36" s="9">
         <v>117.24137930000001</v>
@@ -5278,10 +5268,10 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C37" s="9">
         <v>103.9215686</v>
@@ -5293,10 +5283,10 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C38" s="9">
         <v>127.50665714285709</v>
@@ -5310,10 +5300,10 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C39" s="9">
         <v>99.910941428571434</v>
@@ -5327,10 +5317,10 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C40" s="9">
         <v>129.86775</v>
@@ -5344,10 +5334,10 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C41" s="9">
         <v>103.78951499999999</v>
@@ -5361,10 +5351,10 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C42" s="9">
         <v>179.78720000000001</v>
@@ -5376,10 +5366,10 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C43" s="9">
         <v>105.9288538</v>
@@ -5391,10 +5381,10 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C44" s="8">
         <v>6.3017471731666674</v>
@@ -5408,10 +5398,10 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C45" s="8">
         <v>6.5602791480000002</v>
@@ -5425,10 +5415,10 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C46" s="8">
         <v>6.184586267857143</v>
@@ -5442,10 +5432,10 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C47" s="8">
         <v>6.8102426964999996</v>
@@ -5459,10 +5449,10 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C48" s="8">
         <v>6.2776852359999999</v>
@@ -5476,10 +5466,10 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C49" s="8">
         <v>6.4431933939999997</v>
@@ -5491,10 +5481,10 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C50" s="8">
         <v>6.6792430774999998</v>
@@ -5508,10 +5498,10 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C51" s="8">
         <v>6.0780931322857148</v>
@@ -5525,10 +5515,10 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C52" s="8">
         <v>5.4422112107142846</v>
@@ -5542,10 +5532,10 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C53" s="8">
         <v>0</v>
@@ -5559,10 +5549,10 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C54" s="8">
         <v>6.2418321754999999</v>
@@ -5576,10 +5566,10 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C55" s="8">
         <v>6.6215666879999997</v>
@@ -5617,75 +5607,75 @@
   <sheetData>
     <row r="1" spans="1:17" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="D5" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="F5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="J5" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" s="6" t="s">
+      <c r="K5" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="L5" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="M5" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="N5" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="O5" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="P5" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="Q5" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="P5" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q5" s="6" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B6" s="9">
         <v>22.78382974110713</v>
@@ -5738,7 +5728,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B7" s="12">
         <v>13.90511990848491</v>
@@ -5791,7 +5781,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B8" s="9">
         <v>64.552025833734461</v>
@@ -5844,7 +5834,7 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B9" s="8">
         <v>8.3938535064090587</v>
@@ -5897,7 +5887,7 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B10" s="9">
         <v>10.457202863070849</v>
@@ -5950,7 +5940,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B11" s="8">
         <v>1.7052668632133461</v>
@@ -6003,7 +5993,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B12" s="8">
         <v>5.5764837502730842</v>
@@ -6056,7 +6046,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B13" s="9">
         <v>46.697454100692482</v>
@@ -6109,7 +6099,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B14" s="8">
         <v>2.6468189118021002</v>
@@ -6162,7 +6152,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B15" s="9">
         <v>20.758774029121039</v>
@@ -6215,7 +6205,7 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B16" s="8">
         <v>4.8627414752931912</v>
@@ -6268,7 +6258,7 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B17" s="8">
         <v>9.6974229110668588</v>
@@ -6321,7 +6311,7 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B18" s="8">
         <v>7.6992278925817033</v>
@@ -6374,7 +6364,7 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B19" s="8">
         <v>1.302706797908558</v>
@@ -6427,7 +6417,7 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B20" s="8">
         <v>7.3583690136003383</v>
@@ -6480,7 +6470,7 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B21" s="8">
         <v>1.767500803715407</v>
@@ -6533,7 +6523,7 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B22" s="8">
         <v>0.2666630843536808</v>
@@ -6586,7 +6576,7 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B23" s="8">
         <v>5.4827632317725588</v>
@@ -6639,7 +6629,7 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B24" s="8">
         <v>5.2818789328988913</v>
@@ -6692,7 +6682,7 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B25" s="8">
         <v>8.3626322683055108</v>
@@ -6745,7 +6735,7 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B26" s="8">
         <v>1.5055539516369121</v>
@@ -6798,7 +6788,7 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B27" s="8">
         <v>2.8835021018024491</v>
@@ -6851,7 +6841,7 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B28" s="9">
         <v>11.86038664184475</v>
@@ -6904,7 +6894,7 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B29" s="8">
         <v>3.5649386839632631</v>
@@ -6957,7 +6947,7 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B30" s="9">
         <v>18.743825271960169</v>
@@ -7010,7 +7000,7 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B31" s="8">
         <v>2.5039715066285559</v>
@@ -7063,7 +7053,7 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B32" s="8">
         <v>6.4357909216199563</v>
@@ -7116,65 +7106,65 @@
     </row>
     <row r="35" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C36" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="D36" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="F36" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I36" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D36" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E36" s="6" t="s">
+      <c r="J36" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="F36" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="I36" s="6" t="s">
+      <c r="K36" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="J36" s="6" t="s">
+      <c r="L36" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K36" s="6" t="s">
+      <c r="M36" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="L36" s="6" t="s">
+      <c r="N36" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="M36" s="6" t="s">
+      <c r="O36" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="N36" s="6" t="s">
+      <c r="P36" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="O36" s="6" t="s">
+      <c r="Q36" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="P36" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q36" s="6" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B37" s="9">
         <v>20.833453033961749</v>
@@ -7227,7 +7217,7 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B38" s="8">
         <v>4.3703810962565228</v>
@@ -7280,7 +7270,7 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B39" s="9">
         <v>10.26094304326489</v>
@@ -7333,7 +7323,7 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B40" s="8">
         <v>0.90276442993878447</v>
@@ -7386,7 +7376,7 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A41" s="11" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B41" s="13">
         <v>8.0313156483812591</v>
@@ -7439,7 +7429,7 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B42" s="9">
         <v>50.024410287773577</v>
@@ -7492,7 +7482,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B43" s="8">
         <v>4.480204499670478</v>
@@ -7545,7 +7535,7 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B44" s="9">
         <v>16.82100352097623</v>
@@ -7598,7 +7588,7 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B45" s="8">
         <v>3.4731777244867601</v>
@@ -7651,7 +7641,7 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B46" s="8">
         <v>4.8439432071896249</v>
@@ -7704,7 +7694,7 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B47" s="9">
         <v>10.536108819127881</v>
@@ -7757,7 +7747,7 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B48" s="8">
         <v>0.1483305835729922</v>
@@ -7810,7 +7800,7 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B49" s="8">
         <v>7.612313113746751</v>
@@ -7863,7 +7853,7 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B50" s="8">
         <v>7.8464819643859576</v>
@@ -7916,7 +7906,7 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B51" s="8">
         <v>7.4258018731142101</v>
@@ -7969,7 +7959,7 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A52" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B52" s="8">
         <v>3.145713766329834</v>
@@ -8022,7 +8012,7 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A53" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B53" s="9">
         <v>11.350718361313421</v>
@@ -8075,7 +8065,7 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A54" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B54" s="8">
         <v>2.434850466605631</v>
@@ -8128,7 +8118,7 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A55" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B55" s="9">
         <v>18.137184106021731</v>
@@ -8181,7 +8171,7 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A56" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B56" s="8">
         <v>1.7029634594259979</v>
@@ -8252,53 +8242,53 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="H6" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B7" s="11">
         <v>38</v>
@@ -8324,7 +8314,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B8" s="11">
         <v>44</v>
@@ -8350,7 +8340,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B9" s="7">
         <v>15</v>
@@ -8376,7 +8366,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B10" s="7">
         <v>9</v>
@@ -8402,7 +8392,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B11" s="11">
         <v>19</v>
@@ -8428,7 +8418,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B12" s="7">
         <v>8</v>
@@ -8454,7 +8444,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B13" s="11">
         <v>52</v>
@@ -8480,7 +8470,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B14" s="7">
         <v>6</v>
@@ -8506,7 +8496,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B15" s="7">
         <v>11</v>
@@ -8532,7 +8522,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B16" s="7">
         <v>5</v>
@@ -8558,7 +8548,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B17" s="7">
         <v>8</v>
@@ -8584,7 +8574,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B18" s="11">
         <v>23</v>
@@ -8610,7 +8600,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B19" s="7">
         <v>6</v>
@@ -8636,7 +8626,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B20" s="7">
         <v>4</v>
@@ -8662,7 +8652,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B21" s="7">
         <v>3</v>
@@ -8688,7 +8678,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B22" s="7">
         <v>4</v>
@@ -8714,7 +8704,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B23" s="7">
         <v>3</v>
@@ -8740,7 +8730,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B24" s="7">
         <v>6</v>
@@ -8766,7 +8756,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B25" s="7">
         <v>4</v>
@@ -8792,7 +8782,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B26" s="7">
         <v>5</v>
@@ -8818,7 +8808,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B27" s="7">
         <v>3</v>
@@ -8844,7 +8834,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B28" s="7">
         <v>2</v>
@@ -8870,7 +8860,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B29" s="7">
         <v>1</v>
@@ -8896,7 +8886,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B30" s="7">
         <v>4</v>
@@ -8922,7 +8912,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B31" s="7">
         <v>5</v>
@@ -8948,7 +8938,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B32" s="7">
         <v>2</v>
@@ -8974,43 +8964,43 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B37" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D37" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="E37" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="F37" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="G37" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="H37" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B38" s="7">
         <v>8</v>
@@ -9036,7 +9026,7 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B39" s="11">
         <v>11</v>
@@ -9062,7 +9052,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B40" s="11">
         <v>9</v>
@@ -9088,7 +9078,7 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B41" s="7">
         <v>5</v>
@@ -9114,7 +9104,7 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B42" s="7">
         <v>1</v>
@@ -9140,7 +9130,7 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B43" s="7">
         <v>3</v>
@@ -9166,7 +9156,7 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B44" s="7">
         <v>1</v>
@@ -9192,7 +9182,7 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B45" s="7">
         <v>1</v>
@@ -9218,7 +9208,7 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B46" s="7">
         <v>2</v>
@@ -9244,7 +9234,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B47" s="7">
         <v>3</v>
@@ -9270,7 +9260,7 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B48" s="7">
         <v>1</v>
@@ -9296,7 +9286,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B49" s="7">
         <v>2</v>
@@ -9322,7 +9312,7 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B50" s="7">
         <v>1</v>
@@ -9348,7 +9338,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B51" s="7">
         <v>4</v>
@@ -9374,7 +9364,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B52" s="7">
         <v>1</v>
@@ -9418,58 +9408,58 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="E8" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>162</v>
-      </c>
       <c r="G8" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B9" s="11">
         <v>46</v>
@@ -9495,7 +9485,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B10" s="11">
         <v>61</v>
@@ -9521,7 +9511,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B11" s="11">
         <v>24</v>
@@ -9547,7 +9537,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B12" s="11">
         <v>12</v>
@@ -9573,7 +9563,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B13" s="11">
         <v>23</v>
@@ -9599,7 +9589,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B14" s="11">
         <v>9</v>
@@ -9625,7 +9615,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B15" s="11">
         <v>66</v>
@@ -9651,7 +9641,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B16" s="7">
         <v>7</v>
@@ -9677,7 +9667,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B17" s="11">
         <v>12</v>
@@ -9703,7 +9693,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B18" s="7">
         <v>3</v>
@@ -9729,7 +9719,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B19" s="11">
         <v>9</v>
@@ -9755,7 +9745,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B20" s="11">
         <v>25</v>
@@ -9781,7 +9771,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B21" s="11">
         <v>7</v>
@@ -9807,7 +9797,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B22" s="7">
         <v>4</v>
@@ -9833,7 +9823,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B23" s="7">
         <v>2</v>
@@ -9859,7 +9849,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B24" s="7">
         <v>7</v>
@@ -9885,7 +9875,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B25" s="11">
         <v>5</v>
@@ -9911,7 +9901,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B26" s="11">
         <v>9</v>
@@ -9937,7 +9927,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="11" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B27" s="11">
         <v>9</v>
@@ -9963,7 +9953,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B28" s="11">
         <v>6</v>
@@ -9989,7 +9979,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B29" s="7">
         <v>8</v>
@@ -10015,7 +10005,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B30" s="11">
         <v>5</v>
@@ -10041,7 +10031,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B31" s="7">
         <v>1</v>
@@ -10067,7 +10057,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B32" s="7">
         <v>2</v>
@@ -10093,7 +10083,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B33" s="7">
         <v>5</v>
@@ -10119,7 +10109,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B34" s="7">
         <v>2</v>
@@ -10170,75 +10160,75 @@
   <sheetData>
     <row r="1" spans="1:15" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="F5" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G5" s="6" t="s">
+      <c r="I5" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="J5" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="K5" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="L5" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="M5" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="N5" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="O5" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>178</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>180</v>
       </c>
       <c r="D6" s="9">
         <v>23.401256549537241</v>
@@ -10279,38 +10269,38 @@
     </row>
     <row r="9" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D11" s="8">
         <v>1.557154244910665</v>
@@ -10324,13 +10314,13 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D12" s="8">
         <v>0.96415949443495963</v>
@@ -10344,13 +10334,13 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D13" s="8">
         <v>1.744826321728238</v>
@@ -10364,46 +10354,46 @@
     </row>
     <row r="16" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E18" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="H18" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C19" s="9">
         <v>10.62120218244316</v>
@@ -10426,10 +10416,10 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C20" s="9">
         <v>30.564053822359028</v>
@@ -10452,44 +10442,44 @@
     </row>
     <row r="23" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="D24" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="F24" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E24" s="6" t="s">
+      <c r="G24" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="I24" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="G24" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>195</v>
-      </c>
       <c r="J24" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B25" s="8">
         <v>0.35868698757926709</v>
@@ -10521,7 +10511,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B26" s="8">
         <v>0.41333917227112221</v>
@@ -10553,49 +10543,49 @@
     </row>
     <row r="29" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B31" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="D31" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="F31" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="G31" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="H31" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="6" t="s">
+      <c r="I31" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C32" s="8">
         <v>8.5021069536428122</v>
@@ -10621,32 +10611,32 @@
     </row>
     <row r="35" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C36" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C37" s="8">
         <v>5.2936095249527818E-2</v>
@@ -10660,10 +10650,10 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="7" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C38" s="8">
         <v>5.3939312207303497E-2</v>
@@ -10677,10 +10667,10 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C39" s="8">
         <v>4.8279966116282033E-2</v>
@@ -10712,39 +10702,39 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="E5" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B6" s="9">
         <v>163.11323798966399</v>
@@ -10761,20 +10751,20 @@
     </row>
     <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B11" s="10">
         <v>1.5698989120498179E-33</v>
@@ -10782,7 +10772,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B12" s="8">
         <v>2.0563489435455099E-3</v>
@@ -10790,7 +10780,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B13" s="8">
         <v>8.4721829816905472E-4</v>
@@ -10798,7 +10788,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B14" s="10">
         <v>1.633333087432134E-28</v>
@@ -10806,7 +10796,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B15" s="10">
         <v>1.1905970165436419E-27</v>
@@ -10814,7 +10804,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B16" s="8">
         <v>0.75135631313647766</v>
@@ -10822,35 +10812,35 @@
     </row>
     <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C20" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>65</v>
-      </c>
       <c r="F20" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C21" s="8">
         <v>0.32032280149343101</v>
@@ -10865,10 +10855,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>217</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>219</v>
       </c>
       <c r="C22" s="8">
         <v>0.77803558120645377</v>
@@ -10883,10 +10873,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C23" s="8">
         <v>0.39304750016401052</v>
@@ -10901,10 +10891,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C24" s="8">
         <v>0.40039845677178421</v>
@@ -10938,54 +10928,54 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="I5" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C6" s="8">
         <v>4.2556723108468431</v>
@@ -11011,32 +11001,32 @@
     </row>
     <row r="9" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C10" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C11" s="8">
         <v>0.50070750213537829</v>
@@ -11050,10 +11040,10 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C12" s="8">
         <v>0.56098175329837918</v>
@@ -11067,10 +11057,10 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C13" s="8">
         <v>0.46479055332343711</v>
@@ -11084,44 +11074,44 @@
     </row>
     <row r="16" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="D17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="F17" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="G17" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="H17" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="I17" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C18" s="9">
         <v>10.80028694489299</v>
@@ -11147,10 +11137,10 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C19" s="8">
         <v>5.6825165761963996</v>
@@ -11176,32 +11166,32 @@
     </row>
     <row r="22" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C23" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C24" s="8">
         <v>0.13761968728943269</v>
@@ -11215,10 +11205,10 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C25" s="8">
         <v>0.1556307568136393</v>
@@ -11232,10 +11222,10 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C26" s="8">
         <v>0.14173409209489929</v>
@@ -11249,10 +11239,10 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C27" s="8">
         <v>7.574523890309065E-2</v>
@@ -11266,10 +11256,10 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C28" s="8">
         <v>8.2632490896628497E-2</v>
@@ -11283,10 +11273,10 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C29" s="8">
         <v>7.3955570170383456E-2</v>
@@ -11300,44 +11290,44 @@
     </row>
     <row r="32" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B33" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="D33" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E33" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="F33" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="G33" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="H33" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="I33" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C34" s="8">
         <v>5.7533412476945784</v>
@@ -11363,32 +11353,32 @@
     </row>
     <row r="37" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C38" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E38" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C39" s="8">
         <v>0.12687227353474911</v>
@@ -11402,10 +11392,10 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C40" s="8">
         <v>0.13152635289953021</v>
@@ -11419,10 +11409,10 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C41" s="8">
         <v>0.1212945346788382</v>
